--- a/results/job_matches_2026-06-12.xlsx
+++ b/results/job_matches_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer-Marketing Technology</t>
+          <t>Sr. Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Foxit</t>
+          <t>Personalis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
+          <t>https://www.indeed.com/viewjob?jk=bb348c14b73d98a3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud Infrastructure</t>
+          <t>Data Engineer-Marketing Technology</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Personalis</t>
+          <t>Foxit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb348c14b73d98a3</t>
+          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1d2f0b19c98908</t>
+          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Allied Solutions</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, Medallion Architecture, GCP, Hadoop, Hive, Spark</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444d7dbb36b2d6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=be1d2f0b19c98908</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Development/Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Dataflow, Vertex AI, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3530403779aaafd2</t>
+          <t>https://www.indeed.com/viewjob?jk=d1491ce2afe6000a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, HBase, Spark</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1491ce2afe6000a</t>
+          <t>https://www.indeed.com/viewjob?jk=b8327d885674c2cb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Operations Engineer (Site Reliability Engineer)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8327d885674c2cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0928cac745f837eb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Platform Operations Engineer (Site Reliability Engineer)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>MEDecision</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0928cac745f837eb</t>
+          <t>https://www.indeed.com/viewjob?jk=19beaee823c8d513</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Data Engineer (Hybrid Eligible*)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEDecision</t>
+          <t>WaFd Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19beaee823c8d513</t>
+          <t>https://www.indeed.com/viewjob?jk=676157bc1afd24c8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer/Associate</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Seattle Children's</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe630ebf9cbab80</t>
+          <t>https://www.indeed.com/viewjob?jk=147df69fbd3dc06f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid Eligible*)</t>
+          <t>Sr. Specialist, Yield Management - GTM AA Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Kafka, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676157bc1afd24c8</t>
+          <t>https://www.indeed.com/viewjob?jk=22786462c04357ed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Yield Management - GTM AA Software Engineer</t>
+          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Full Swing Golf Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Kafka, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22786462c04357ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
+          <t>https://www.indeed.com/viewjob?jk=04ed95a8ab7c02d2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
+          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
+          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
+          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
+          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
+          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
+          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Riot Platforms, Inc.</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, Timestream, RDS, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb33b9b74da3225</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Recursion Technologies, Inc</t>
+          <t>Riot Platforms, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, Timestream, RDS, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb33b9b74da3225</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec9eccd457d1c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Cloud Security Engineer/DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>GetWellNetwork</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, MySQL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbd6697aef07bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>o9 Solutions</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hadoop, Hive, Sqoop, Oozie, Zookeeper, YARN, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf300316a739534d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b5608a7f41b4e3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Databricks Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Franklin Park, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, RDS, Databricks, Hadoop, Hive, YARN</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928d0dbf6d50f764</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec9eccd457d1c7e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Recursion Technologies, Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
+          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
+          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>I2E Consulting Pvt Ltd</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Glue, EMR, S3, SQS, RDS, Databricks, Hadoop, Hive, YARN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650af1c5e8c39884</t>
+          <t>https://www.indeed.com/viewjob?jk=928d0dbf6d50f764</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Architect (IGEN)</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=657d301f2f1b7537</t>
+          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Quality Assurance (QA) Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>I2E Consulting Pvt Ltd</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47abd28c0aa248a7</t>
+          <t>https://www.indeed.com/viewjob?jk=650af1c5e8c39884</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Quality Assurance (QA) Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=973ffbc88d0c427a</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbd6697aef07bb4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Quality Assurance (QA) Engineer</t>
+          <t>Cloud Architect (IGEN)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf0524e41351a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=657d301f2f1b7537</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quality Assurance (QA) Engineer</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, CodeBuild</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91c9d41b3a88a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b38a31f90568f6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, CodeBuild</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b38a31f90568f6</t>
+          <t>https://www.indeed.com/viewjob?jk=287c3f75cf52bffd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287c3f75cf52bffd</t>
+          <t>https://www.indeed.com/viewjob?jk=47abd28c0aa248a7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MPR Management</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Flint, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
+          <t>https://www.indeed.com/viewjob?jk=973ffbc88d0c427a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf0524e41351a6c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enterprise Architect – R01566150</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac2a0315c25f7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b91c9d41b3a88a9c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Constellation Software, Inc.</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,137 +2281,137 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analyst, Enterprise Data</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MCLEOD SOFTWARE</t>
+          <t>MPR Management</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Flint, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
+          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer with Python and React - Remote</t>
+          <t>Enterprise Architect – R01566150</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc2b0d080f003ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac2a0315c25f7a8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
+          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Database Platform Distinguished Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Constellation Software, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1878bb369b786a4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Analyst, Enterprise Data</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>MCLEOD SOFTWARE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b576fbb7c24544a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd643ae862f32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=dcffbd042483fd6d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Spark, PySpark, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f77ff3e5347e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a73bb9e4fcd1194d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Data Architect, Databricks</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Photon, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4998cd152a5e1f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ef01ac70d36eca</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Appian Developer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Makpar Corporation</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,962 +2586,2082 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
+          <t>https://www.indeed.com/viewjob?jk=af0f3caaa77dc460</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d3e7e600902d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c6411ff02f3373c0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe5dcd6edbb6191</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Stock Yards Bank &amp; Trust</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce0334c84fa0af8d</t>
+          <t>https://www.indeed.com/viewjob?jk=4406ca67f5f7436a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau and Affiliated Companies</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c035ca05535e9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c6a5b0eda2e3405</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Analytics Data Platform Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60b7462f872f2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=71f5e7eba845df7f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c98ea64c47e01e6</t>
+          <t>https://www.indeed.com/viewjob?jk=382e7b658e71f3b4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff9fec023b73eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=4f91e0a343a737cd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AlpacaJapan株式会社</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b7132352f20af8</t>
+          <t>https://www.indeed.com/viewjob?jk=875b6972437ebd32</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Product Engineer Data &amp; AI</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a86b284f45948d1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f876573743957d0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site Contract</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e87af5630fd7111</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7303d62b7d5ce7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineers (Golang/Java)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TECHNOLOGENT</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c62cabc105423e67</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
+          <t>https://www.indeed.com/viewjob?jk=0f98fa430296daa1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
+          <t>https://www.indeed.com/viewjob?jk=d944735358e10029</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a780fbab7d5b68</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57a86fed30272e5</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf18b0ca49d35a5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Manufacturing)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4bbea5d38dc11d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe164b5bf5a40b2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Charlotte, NC)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
+          <t>https://www.indeed.com/viewjob?jk=50a9d70f95366aad</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Calder</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6dcd0a14bbb7a4</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Peterson Holding</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
+          <t>https://www.indeed.com/viewjob?jk=310b89f9a79e8382</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AlpacaJapan株式会社</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f9bcf7a0cd9dbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2de5436b0de47</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Rochester Electronics</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Newburyport, MA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb77a558047a211</t>
+          <t>https://www.indeed.com/viewjob?jk=300d9f4832f7d438</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Presidio</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, HBase, Scala, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
+          <t>https://www.indeed.com/viewjob?jk=c506c367da32e3ea</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IT Software Application Developer II</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=2e19fb7c6ebabd01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IT Software Application Developer II</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
+          <t>https://www.indeed.com/viewjob?jk=456fb35d0f2a345e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Active IQ Engineering</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
+          <t>https://www.indeed.com/viewjob?jk=b69e6b49a8c83225</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a77f7fc0875b8913</t>
+          <t>https://www.indeed.com/viewjob?jk=44f6f18e275bf4f7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer 2(Java/SpringBoot/Microservices/Kafka)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be8586386e048813</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bf6a320af2700c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=037518cf796f2c26</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90ea1fa1ffbbfbda</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22ef31fe96b1f9e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ed4c13455f9ce86</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Gap Inc.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Appian Developer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Makpar Corporation</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Stock Yards Bank &amp; Trust</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce0334c84fa0af8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Texas Farm Bureau and Affiliated Companies</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Waco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c035ca05535e9d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>DoubleVerify</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d60b7462f872f2e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74d3e7e600902d7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Texas Farm Bureau - Insurance Agents</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Waco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c98ea64c47e01e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AssetMark</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Snowflake, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ff9fec023b73eaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>AlpacaJapan株式会社</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Google Cloud Platform, GCP, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45b7132352f20af8</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Engineers (Golang/Java)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TECHNOLOGENT</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>DevOps &amp; Tools Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DevOps &amp; Tools Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>DevOps &amp; Tools Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Camas, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Platform</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Calder</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
         <v>10.4</v>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fae5dae15c5081c</t>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Peterson Holding</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>San Leandro, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior PySpark Data Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d57a86fed30272e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer (Manufacturing)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ion Storage Systems</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Beltsville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a4bbea5d38dc11d</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer (Charlotte, NC)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>AlpacaJapan株式会社</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5f9bcf7a0cd9dbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a51301d84047381d</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Rochester Electronics</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Newburyport, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4eb77a558047a211</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>IT Software Application Developer II</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>IT Software Application Developer II</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Associate Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Presidio</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, Azure, HBase, Scala, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer - Active IQ Engineering</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NetApp</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-12.xlsx
+++ b/results/job_matches_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud Infrastructure</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Personalis</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb348c14b73d98a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Sr. Software Engineer, Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Personalis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb348c14b73d98a3</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Hive, HBase, Spark</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1491ce2afe6000a</t>
+          <t>https://www.indeed.com/viewjob?jk=b8327d885674c2cb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer - Python / DevOps / Message Brokers</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8327d885674c2cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ccd83a736eef1f</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid Eligible*)</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WaFd Bank</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=676157bc1afd24c8</t>
+          <t>https://www.indeed.com/viewjob?jk=147df69fbd3dc06f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Sr. Specialist, Yield Management - GTM AA Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Kafka, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147df69fbd3dc06f</t>
+          <t>https://www.indeed.com/viewjob?jk=22786462c04357ed</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Yield Management - GTM AA Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Kafka, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22786462c04357ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Full Swing Golf Inc</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
+          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ed95a8ab7c02d2</t>
+          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
+          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
+          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
+          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
+          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
+          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
+          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
+          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Full Swing Golf Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
+          <t>https://www.indeed.com/viewjob?jk=04ed95a8ab7c02d2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
+          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Riot Platforms, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>Redshift, Timestream, RDS, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb33b9b74da3225</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Riot Platforms, Inc.</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, Timestream, RDS, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling, Snowflake Schema</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb33b9b74da3225</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Security Engineer/DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>GetWellNetwork</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer/DevSecOps Engineer</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GetWellNetwork</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b5608a7f41b4e3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Recursion Technologies, Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
+          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b5608a7f41b4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
         </is>
       </c>
     </row>
@@ -1833,25 +1833,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Recursion Technologies, Inc</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbd6697aef07bb4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Application Developer – Data &amp; Digital Solutions</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>TC Energy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, RDS, Databricks, Hadoop, Hive, YARN</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928d0dbf6d50f764</t>
+          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, S3, SQS, RDS, Databricks, Hadoop, Hive, YARN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
+          <t>https://www.indeed.com/viewjob?jk=928d0dbf6d50f764</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I2E Consulting Pvt Ltd</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650af1c5e8c39884</t>
+          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>I2E Consulting Pvt Ltd</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbd6697aef07bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=650af1c5e8c39884</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Jenkins, CodeBuild</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b38a31f90568f6</t>
+          <t>https://www.indeed.com/viewjob?jk=287c3f75cf52bffd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>MPR Management</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Flint, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287c3f75cf52bffd</t>
+          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quality Assurance (QA) Engineer</t>
+          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47abd28c0aa248a7</t>
+          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Quality Assurance (QA) Engineer</t>
+          <t>Enterprise Architect – R01566150</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=973ffbc88d0c427a</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac2a0315c25f7a8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Quality Assurance (QA) Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf0524e41351a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Quality Assurance (QA) Engineer</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91c9d41b3a88a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>Constellation Software, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Analyst, Enterprise Data</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MPR Management</t>
+          <t>MCLEOD SOFTWARE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Flint, MI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
+          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Enterprise Architect – R01566150</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac2a0315c25f7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Appian Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Makpar Corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Constellation Software, Inc.</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analyst, Enterprise Data</t>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MCLEOD SOFTWARE</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,417 +2456,417 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
+          <t>https://www.indeed.com/viewjob?jk=74d3e7e600902d7a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcffbd042483fd6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Bridgepointe Technologies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73bb9e4fcd1194d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e6e1623e260b65</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Stock Yards Bank &amp; Trust</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ef01ac70d36eca</t>
+          <t>https://www.indeed.com/viewjob?jk=ce0334c84fa0af8d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Texas Farm Bureau and Affiliated Companies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0f3caaa77dc460</t>
+          <t>https://www.indeed.com/viewjob?jk=3c035ca05535e9d0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr. Analytics Data Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6411ff02f3373c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d60b7462f872f2e3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe5dcd6edbb6191</t>
+          <t>https://www.indeed.com/viewjob?jk=9c98ea64c47e01e6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Snowflake, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4406ca67f5f7436a</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff9fec023b73eaf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Software Engineers (Golang/Java)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>TECHNOLOGENT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c6a5b0eda2e3405</t>
+          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f5e7eba845df7f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=382e7b658e71f3b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>DevOps &amp; Tools Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Camas, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f91e0a343a737cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,207 +2876,207 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875b6972437ebd32</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f876573743957d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d57a86fed30272e5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Platform Engineer (Manufacturing)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7303d62b7d5ce7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4bbea5d38dc11d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr. Data Engineer (Charlotte, NC)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c62cabc105423e67</t>
+          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Calder</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f98fa430296daa1</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Peterson Holding</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d944735358e10029</t>
+          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,1582 +3086,182 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a780fbab7d5b68</t>
+          <t>https://www.indeed.com/viewjob?jk=a51301d84047381d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>IT Software Application Developer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf18b0ca49d35a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>IT Software Application Developer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe164b5bf5a40b2</t>
+          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Associate Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Presidio</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, HBase, Scala, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a9d70f95366aad</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Full Stack Engineer - Active IQ Engineering</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6dcd0a14bbb7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Rochester Electronics</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Newburyport, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310b89f9a79e8382</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2de5436b0de47</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=300d9f4832f7d438</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c506c367da32e3ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e19fb7c6ebabd01</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=456fb35d0f2a345e</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b69e6b49a8c83225</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44f6f18e275bf4f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be8586386e048813</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf6a320af2700c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=037518cf796f2c26</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90ea1fa1ffbbfbda</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22ef31fe96b1f9e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ed4c13455f9ce86</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Gap Inc.</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>SC, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Appian Developer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Makpar Corporation</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Palo Alto Networks</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Stock Yards Bank &amp; Trust</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce0334c84fa0af8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Texas Farm Bureau and Affiliated Companies</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Waco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c035ca05535e9d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>DoubleVerify</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d60b7462f872f2e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74d3e7e600902d7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Waco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c98ea64c47e01e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>AssetMark</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Snowflake, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff9fec023b73eaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>AlpacaJapan株式会社</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, GCP, Spark, Scala, Kafka, ETL, dbt, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=45b7132352f20af8</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Software Engineers (Golang/Java)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>TECHNOLOGENT</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>DevOps &amp; Tools Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Qode</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>DevOps &amp; Tools Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Qode</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>DevOps &amp; Tools Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Qode</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Camas, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Platform</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Calder</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Peterson Holding</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>San Leandro, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior PySpark Data Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d57a86fed30272e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer (Manufacturing)</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Ion Storage Systems</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Beltsville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4bbea5d38dc11d</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer (Charlotte, NC)</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>The Hartford</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>AlpacaJapan株式会社</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f9bcf7a0cd9dbd</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a51301d84047381d</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Enterprise Data Architect</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Rochester Electronics</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Newburyport, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=4eb77a558047a211</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>IT Software Application Developer II</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>IT Software Application Developer II</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Associate Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Presidio</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Azure, HBase, Scala, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer - Active IQ Engineering</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>NetApp</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-12.xlsx
+++ b/results/job_matches_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Software Engineer III: Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,29 +701,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
+          <t>https://www.indeed.com/viewjob?jk=5309dfbe88757dfa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer-Marketing Technology</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Foxit</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66618d4a082a7f22</t>
+          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
         </is>
       </c>
     </row>
@@ -1798,25 +1798,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Databricks Developer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Franklin Park, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec9eccd457d1c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbd6697aef07bb4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Application Developer – Data &amp; Digital Solutions</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>TC Energy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbd6697aef07bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Application Developer – Data &amp; Digital Solutions</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TC Energy</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, S3, SQS, RDS, Databricks, Hadoop, Hive, YARN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
+          <t>https://www.indeed.com/viewjob?jk=928d0dbf6d50f764</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, RDS, Databricks, Hadoop, Hive, YARN</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928d0dbf6d50f764</t>
+          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Cloud Architect (IGEN)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
+          <t>IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
+          <t>https://www.indeed.com/viewjob?jk=657d301f2f1b7537</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Backend AWS Engineer (Python)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>I2E Consulting Pvt Ltd</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650af1c5e8c39884</t>
+          <t>https://www.indeed.com/viewjob?jk=d50ab53a04614947</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Architect (IGEN)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=657d301f2f1b7537</t>
+          <t>https://www.indeed.com/viewjob?jk=287c3f75cf52bffd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>MPR Management</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Flint, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287c3f75cf52bffd</t>
+          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MPR Management</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Flint, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
+          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Enterprise Architect – R01566150</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Constellation Software, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac2a0315c25f7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Analyst, Enterprise Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Constellation Software, Inc.</t>
+          <t>MCLEOD SOFTWARE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analyst, Enterprise Data</t>
+          <t>Appian Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MCLEOD SOFTWARE</t>
+          <t>Makpar Corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
+          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
         </is>
       </c>
     </row>
@@ -2358,52 +2358,52 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Appian Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Makpar Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
+          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d3e7e600902d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineers (Golang/Java)</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TECHNOLOGENT</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
+          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f00f70f3712a077</t>
+          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c9c5b96552b007</t>
+          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevOps &amp; Tools Engineer</t>
+          <t>Software Engineers (Golang/Java)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>TECHNOLOGENT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Camas, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, MySQL, MongoDB, Splunk, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ab3fddd487ed32</t>
+          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51301d84047381d</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IT Software Application Developer II</t>
+          <t>Software Engineer, Cloud - E2E Test</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Cassandra, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=126f8c878f1253f3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IT Software Application Developer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
+          <t>https://www.indeed.com/viewjob?jk=a51301d84047381d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Presidio</t>
+          <t>Rochester Electronics</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Newburyport, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, HBase, Scala, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb77a558047a211</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Active IQ Engineering</t>
+          <t>IT Software Application Developer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92b98f547184206</t>
+          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>IT Software Application Developer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rochester Electronics</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Newburyport, MA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,42 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb77a558047a211</t>
+          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Associate Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Presidio</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Azure, HBase, Scala, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-12.xlsx
+++ b/results/job_matches_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8327d885674c2cb</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9e656d2a85bee5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Python / DevOps / Message Brokers</t>
+          <t>Platform Operations Engineer (Site Reliability Engineer)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ccd83a736eef1f</t>
+          <t>https://www.indeed.com/viewjob?jk=0928cac745f837eb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Platform Operations Engineer (Site Reliability Engineer)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0928cac745f837eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b8327d885674c2cb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Sr Software Engineer - Python / DevOps / Message Brokers</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MEDecision</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19beaee823c8d513</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ccd83a736eef1f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>MEDecision</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147df69fbd3dc06f</t>
+          <t>https://www.indeed.com/viewjob?jk=19beaee823c8d513</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Yield Management - GTM AA Software Engineer</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Kafka, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22786462c04357ed</t>
+          <t>https://www.indeed.com/viewjob?jk=147df69fbd3dc06f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Specialist, Yield Management - GTM AA Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Kafka, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
+          <t>https://www.indeed.com/viewjob?jk=22786462c04357ed</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
+          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
+          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
+          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
+          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
+          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
+          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
+          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
+          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Full Swing Golf Inc</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
+          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Full Swing Golf Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ed95a8ab7c02d2</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=04ed95a8ab7c02d2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Riot Platforms, Inc.</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, Timestream, RDS, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb33b9b74da3225</t>
+          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>Riot Platforms, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>Redshift, Timestream, RDS, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb33b9b74da3225</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer/DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GetWellNetwork</t>
+          <t>REPLY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>Cloud Security Engineer/DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>GetWellNetwork</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b5608a7f41b4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Recursion Technologies, Inc</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b5608a7f41b4e3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Recursion Technologies, Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, MySQL</t>
+          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbd6697aef07bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Application Developer – Data &amp; Digital Solutions</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TC Energy</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
+          <t>https://www.indeed.com/viewjob?jk=cfbd6697aef07bb4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Application Developer – Data &amp; Digital Solutions</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>TC Energy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, RDS, Databricks, Hadoop, Hive, YARN</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928d0dbf6d50f764</t>
+          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, S3, SQS, RDS, Databricks, Hadoop, Hive, YARN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcf6f0e1abb4826a</t>
+          <t>https://www.indeed.com/viewjob?jk=928d0dbf6d50f764</t>
         </is>
       </c>
     </row>
@@ -2008,35 +2008,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287c3f75cf52bffd</t>
+          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>Scientific Games</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Solutions Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Constellation Software, Inc.</t>
+          <t>GEM Technologies, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a20d25715f64218c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,77 +2201,77 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
+          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analyst, Enterprise Data</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MCLEOD SOFTWARE</t>
+          <t>Constellation Software, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
+          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Appian Developer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Makpar Corporation</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
+          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,42 +2316,42 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
+          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Full-Stack Engineer - Albany</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>Rocket Science Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
+          <t>https://www.indeed.com/viewjob?jk=919305a6d33188b3</t>
         </is>
       </c>
     </row>
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
+          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Analyst, Enterprise Data</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MCLEOD SOFTWARE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
+          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer II - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Appian Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Makpar Corporation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bridgepointe Technologies</t>
+          <t>Gap Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e6e1623e260b65</t>
+          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Stock Yards Bank &amp; Trust</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce0334c84fa0af8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau and Affiliated Companies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c035ca05535e9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Analytics Data Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60b7462f872f2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c98ea64c47e01e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff9fec023b73eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Bridgepointe Technologies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e6e1623e260b65</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stock Yards Bank &amp; Trust</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce0334c84fa0af8d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Texas Farm Bureau and Affiliated Companies</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
+          <t>https://www.indeed.com/viewjob?jk=3c035ca05535e9d0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineers (Golang/Java)</t>
+          <t>Sr. Analytics Data Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TECHNOLOGENT</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d60b7462f872f2e3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
+          <t>https://www.indeed.com/viewjob?jk=9c98ea64c47e01e6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Snowflake, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,137 +2911,137 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57a86fed30272e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6ff9fec023b73eaf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Manufacturing)</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4bbea5d38dc11d</t>
+          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Charlotte, NC)</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
+          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Calder</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
+          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Software Engineers (Golang/Java)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Peterson Holding</t>
+          <t>TECHNOLOGENT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
+          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud - E2E Test</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Cassandra, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126f8c878f1253f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d57a86fed30272e5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer (Manufacturing)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51301d84047381d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4bbea5d38dc11d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. Data Engineer (Charlotte, NC)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rochester Electronics</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Newburyport, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb77a558047a211</t>
+          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IT Software Application Developer II</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Paylink Direct</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IT Software Application Developer II</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Calder</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Presidio</t>
+          <t>Peterson Holding</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,332 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Services Architect - New York</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a22e754adf0a78bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer (Java, React, Oracle/MySQL, DevOps)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Netbuilder</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b19eed4d204d2f13</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Data Warehouse Architect</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>USI Insurance Services</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Kimball, Snowflake Schema, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2106609d886859e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Software Engineer, Cloud - E2E Test</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, Kafka, Cassandra, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=126f8c878f1253f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>IT Software Application Developer II</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>IT Software Application Developer II</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Associate Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Presidio</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>AWS, Azure, HBase, Scala, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Rochester Electronics</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Newburyport, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4eb77a558047a211</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-12.xlsx
+++ b/results/job_matches_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III: Data Engineer</t>
+          <t>Sr Software Engineer I - Java - International Card Risk Services Technology</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, GCP, HBase, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5309dfbe88757dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea3d9a3991748c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Software Engineer III: Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,29 +736,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
+          <t>https://www.indeed.com/viewjob?jk=5309dfbe88757dfa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud Infrastructure</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Personalis</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb348c14b73d98a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
         </is>
       </c>
     </row>
@@ -1028,52 +1028,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Specialist, Yield Management - GTM AA Software Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Kafka, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22786462c04357ed</t>
+          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>Full Swing Golf Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
+          <t>https://www.indeed.com/viewjob?jk=04ed95a8ab7c02d2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
+          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
+          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
+          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
+          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
+          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
+          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
+          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Full Swing Golf Inc</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
+          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ed95a8ab7c02d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Security Engineer/DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>REPLY</t>
+          <t>GetWellNetwork</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdf8e3f6e4538a3e</t>
+          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer/DevSecOps Engineer</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GetWellNetwork</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b5608a7f41b4e3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Recursion Technologies, Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
+          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,42 +1791,42 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b5608a7f41b4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Application Developer – Data &amp; Digital Solutions</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Recursion Technologies, Inc</t>
+          <t>TC Energy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Application Developer – Data &amp; Digital Solutions</t>
+          <t>Cloud Architect (IGEN)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TC Energy</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
+          <t>https://www.indeed.com/viewjob?jk=657d301f2f1b7537</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Backend AWS Engineer (Python)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,77 +1921,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, SQS, RDS, Databricks, Hadoop, Hive, YARN</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928d0dbf6d50f764</t>
+          <t>https://www.indeed.com/viewjob?jk=d50ab53a04614947</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Architect (IGEN)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=657d301f2f1b7537</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Backend AWS Engineer (Python)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50ab53a04614947</t>
+          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MPR Management</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Flint, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
+          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
+          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEM Technologies, Inc.</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20d25715f64218c</t>
+          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Constellation Software, Inc.</t>
+          <t>Scientific Games</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
+          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer - Albany</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rocket Science Group</t>
+          <t>MPR Management</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Flint, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=919305a6d33188b3</t>
+          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Solutions Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEM Technologies, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
+          <t>https://www.indeed.com/viewjob?jk=a20d25715f64218c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analyst, Enterprise Data</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MCLEOD SOFTWARE</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca341483d10ac32d</t>
+          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer II - UnderwritingCenter</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
+          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Appian Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Makpar Corporation</t>
+          <t>Constellation Software, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, ETL, Tableau, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c14a2b6762683cda</t>
+          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. ML Engineer – ML &amp; Applied AI</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gap Inc.</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLOps, CI/CD</t>
+          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7037bbae043a99c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
+          <t>Full-Stack Engineer - Albany</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Rocket Science Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
+          <t>https://www.indeed.com/viewjob?jk=919305a6d33188b3</t>
         </is>
       </c>
     </row>
@@ -2582,11 +2582,11 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
+          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>GD169 Senior Software Systems Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ADNET Systems, Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Greenbelt, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, Scala, Dask, DynamoDB, ELT, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,129 +2631,129 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
+          <t>https://www.indeed.com/viewjob?jk=f02363682eba87a1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
+          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
+          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bridgepointe Technologies</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e6e1623e260b65</t>
+          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Operational Support (Co-op)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Stock Yards Bank &amp; Trust</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce0334c84fa0af8d</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau and Affiliated Companies</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c035ca05535e9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Analytics Data Platform Engineer</t>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60b7462f872f2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c98ea64c47e01e6</t>
+          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,29 +2901,29 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ff9fec023b73eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Bridgepointe Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e6e1623e260b65</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stock Yards Bank &amp; Trust</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
+          <t>https://www.indeed.com/viewjob?jk=ce0334c84fa0af8d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineers (Golang/Java)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TECHNOLOGENT</t>
+          <t>Texas Farm Bureau and Affiliated Companies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
+          <t>https://www.indeed.com/viewjob?jk=3c035ca05535e9d0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
+          <t>Sr. Analytics Data Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>DoubleVerify</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
+          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
+          <t>https://www.indeed.com/viewjob?jk=d60b7462f872f2e3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,102 +3121,102 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57a86fed30272e5</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Manufacturing)</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4bbea5d38dc11d</t>
+          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Charlotte, NC)</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
+          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Paylink Direct</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
+          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Software Engineers (Golang/Java)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Calder</t>
+          <t>TECHNOLOGENT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
+          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Peterson Holding</t>
+          <t>Paylink Direct</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
+          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Services Architect - New York</t>
+          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a22e754adf0a78bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (Java, React, Oracle/MySQL, DevOps)</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Netbuilder</t>
+          <t>Calder</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19eed4d204d2f13</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>USI Insurance Services</t>
+          <t>Peterson Holding</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Kimball, Snowflake Schema, ELT, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2106609d886859e3</t>
+          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=d57a86fed30272e5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer, Cloud - E2E Test</t>
+          <t>Data Platform Engineer (Manufacturing)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Ion Storage Systems</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Beltsville, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Cassandra, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=126f8c878f1253f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1a4bbea5d38dc11d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IT Software Application Developer II</t>
+          <t>Sr. Data Engineer (Charlotte, NC)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab8d8cc229c57ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IT Software Application Developer II</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>AmeriGas</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,29 +3531,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee9029e7c364607</t>
+          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Associate Engineer</t>
+          <t>Senior Services Architect - New York</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Presidio</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, HBase, Scala, MySQL, MongoDB, Cassandra, NoSQL, Docker, Git</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcc977ad560dcdfe</t>
+          <t>https://www.indeed.com/viewjob?jk=a22e754adf0a78bd</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Full-Stack Developer (Java, React, Oracle/MySQL, DevOps)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rochester Electronics</t>
+          <t>Netbuilder</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Newburyport, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,122 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Dimensional Modeling, Kimball, dbt, Power BI, Tableau, SQL</t>
+          <t>RDS, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb77a558047a211</t>
+          <t>https://www.indeed.com/viewjob?jk=b19eed4d204d2f13</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Warehouse Architect</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>USI Insurance Services</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Kimball, Snowflake Schema, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2106609d886859e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SQL AND ETL DEVELOPER</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de66891cd1166601</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-12.xlsx
+++ b/results/job_matches_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Bilingual Mandarin required</t>
+          <t>Data Engineer - Target Tech and AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda129dc1d7139ca</t>
+          <t>https://www.indeed.com/viewjob?jk=23d858bb54be62b7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - Bilingual Mandarin required</t>
+          <t>Senior Big Data Engineer (Java, Kafka, Spark, ETL)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Systems Development and Analysis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, Azure, Google Cloud Platform, Hadoop, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=718307efaaa14959</t>
+          <t>https://www.indeed.com/viewjob?jk=4101b4f33c020b4b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - Target Tech and AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>ProcyonIT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d858bb54be62b7</t>
+          <t>https://www.indeed.com/viewjob?jk=816452e4692ec940</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer (Java, Kafka, Spark, ETL)</t>
+          <t>Sr Software Engineer I - Java - International Card Risk Services Technology</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Systems Development and Analysis</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Google Cloud Platform, Hadoop, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, GCP, HBase, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4101b4f33c020b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea3d9a3991748c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Hadoop, Hive</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f94a8c00b79278f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Java - International Card Risk Services Technology</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, GCP, HBase, Scala, Kafka, Oracle</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea3d9a3991748c</t>
+          <t>https://www.indeed.com/viewjob?jk=be1d2f0b19c98908</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III: Data Engineer</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, IAM, RDS, Azure, Event Hubs, Google Cloud Platform, GCP, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,77 +741,77 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5309dfbe88757dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=36099f55f9dfc1ab</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Data &amp; Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, Unity Catalog, Spark, PySpark, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
+          <t>https://www.indeed.com/viewjob?jk=8627b9fa5d939b34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Cloud Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>Intelex</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1d2f0b19c98908</t>
+          <t>https://www.indeed.com/viewjob?jk=f9addd16d08dc466</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEDecision</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19beaee823c8d513</t>
+          <t>https://www.indeed.com/viewjob?jk=147df69fbd3dc06f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147df69fbd3dc06f</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6c83582ab47968</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Full Swing Golf Inc</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
+          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ed95a8ab7c02d2</t>
+          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
+          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
+          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
+          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
+          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
+          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
+          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
+          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Full Swing Golf Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
+          <t>https://www.indeed.com/viewjob?jk=04ed95a8ab7c02d2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Cloud Security Engineer/DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Riot Platforms, Inc.</t>
+          <t>GetWellNetwork</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, Timestream, RDS, Databricks, BigQuery, Scala, Snowflake, Oracle, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb33b9b74da3225</t>
+          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer/DevSecOps Engineer</t>
+          <t>Senior AWS Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GetWellNetwork</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Recursion Technologies, Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, ECS</t>
+          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,42 +1756,42 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b5608a7f41b4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer, Geospatial Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Recursion Technologies, Inc</t>
+          <t>Civitech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
         </is>
       </c>
     </row>
@@ -1833,95 +1833,95 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, MySQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfbd6697aef07bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Architect (IGEN)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U.S. Venture, Inc.</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Appleton, WI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=657d301f2f1b7537</t>
+          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Backend AWS Engineer (Python)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50ab53a04614947</t>
+          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>MPR Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Flint, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
+          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
+          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
+          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
+          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr. Solutions Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MPR Management</t>
+          <t>GEM Technologies, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Flint, MI, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
+          <t>https://www.indeed.com/viewjob?jk=a20d25715f64218c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEM Technologies, Inc.</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20d25715f64218c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
+          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full-Stack Engineer - Albany</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Constellation Software, Inc.</t>
+          <t>Rocket Science Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,77 +2481,77 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, BigQuery, Vertex AI, Snowflake, Data Modeling, ETL</t>
+          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3da1bd303b951ea</t>
+          <t>https://www.indeed.com/viewjob?jk=919305a6d33188b3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
+          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer - Albany</t>
+          <t>AI QA Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rocket Science Group</t>
+          <t>Comtek Intl</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=919305a6d33188b3</t>
+          <t>https://www.indeed.com/viewjob?jk=956ec640e084971c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Specialist Solutions Architect - GCP Infrastructure</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
+          <t>https://www.indeed.com/viewjob?jk=5f18ddccc944039f</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - Operational Support (Co-op)</t>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
+          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
+          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer - Operational Support (Co-op)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bridgepointe Technologies</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e6e1623e260b65</t>
+          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Bridgepointe Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e6e1623e260b65</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau and Affiliated Companies</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c035ca05535e9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Analytics Data Platform Engineer</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DoubleVerify</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Kafka, Snowflake, Dimensional Modeling, Snowflake Schema, dbt, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d60b7462f872f2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c0e35184f1405f1</t>
+          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>Software Engineers (Golang/Java)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>TECHNOLOGENT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AmeriGas</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,59 +3226,59 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineers (Golang/Java)</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TECHNOLOGENT</t>
+          <t>Paylink Direct</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer - Fabric</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Paylink Direct</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
+          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>Calder</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Calder</t>
+          <t>Peterson Holding</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
+          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Business Intelligence Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Peterson Holding</t>
+          <t>Kash Tech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
+          <t>https://www.indeed.com/viewjob?jk=06ab6dcdf3386d55</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior PySpark Data Engineer</t>
+          <t>Senior Services Architect - New York</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57a86fed30272e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a22e754adf0a78bd</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (Manufacturing)</t>
+          <t>Full-Stack Developer (Java, React, Oracle/MySQL, DevOps)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ion Storage Systems</t>
+          <t>Netbuilder</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Beltsville, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, ETL, ELT, Power BI, CI/CD, Docker, Git</t>
+          <t>RDS, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4bbea5d38dc11d</t>
+          <t>https://www.indeed.com/viewjob?jk=b19eed4d204d2f13</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Charlotte, NC)</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>USI Insurance Services</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Scala, Oracle, NoSQL, ETL, Talend, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Kimball, Snowflake Schema, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0624efc6db4599e</t>
+          <t>https://www.indeed.com/viewjob?jk=2106609d886859e3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AmeriGas</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
+          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Services Architect - New York</t>
+          <t>SQL AND ETL DEVELOPER</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3575,146 +3575,6 @@
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a22e754adf0a78bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Full-Stack Developer (Java, React, Oracle/MySQL, DevOps)</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Netbuilder</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b19eed4d204d2f13</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Warehouse Architect</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>USI Insurance Services</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Kimball, Snowflake Schema, ELT, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2106609d886859e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>SQL AND ETL DEVELOPER</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=de66891cd1166601</t>
         </is>

--- a/results/job_matches_2026-06-12.xlsx
+++ b/results/job_matches_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,95 +503,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Target Tech and AI</t>
+          <t>Senior PySpark Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d858bb54be62b7</t>
+          <t>https://www.indeed.com/viewjob?jk=461cc5e336726e29</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer (Java, Kafka, Spark, ETL)</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Systems Development and Analysis</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Google Cloud Platform, Hadoop, HBase, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, Hive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4101b4f33c020b4b</t>
+          <t>https://www.indeed.com/viewjob?jk=041571d1844e3878</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ProcyonIT</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Google Cloud Platform, GCP, Hive, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=816452e4692ec940</t>
+          <t>https://www.indeed.com/viewjob?jk=35e6f9d91bf791b1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Java - International Card Risk Services Technology</t>
+          <t>Data Engineer - Target Tech and AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, GCP, HBase, Scala, Kafka, Oracle</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop, HDFS, Hive, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea3d9a3991748c</t>
+          <t>https://www.indeed.com/viewjob?jk=23d858bb54be62b7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Senior Big Data Engineer (Java, Kafka, Spark, ETL)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Systems Development and Analysis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, Azure, Google Cloud Platform, Hadoop, HBase, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
+          <t>https://www.indeed.com/viewjob?jk=4101b4f33c020b4b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Databricks SME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sprouts Farmers Market</t>
+          <t>Scicom Infrastructure Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT</t>
+          <t>AWS, S3, IAM, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1d2f0b19c98908</t>
+          <t>https://www.indeed.com/viewjob?jk=41d30cbd51be105d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>ProcyonIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, IAM, RDS, Azure, Event Hubs, Google Cloud Platform, GCP, Spark</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36099f55f9dfc1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=816452e4692ec940</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data &amp; Software Engineer</t>
+          <t>Sr Software Engineer I - Java - International Card Risk Services Technology</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, Unity Catalog, Spark, PySpark, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, GCP, HBase, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,242 +776,242 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8627b9fa5d939b34</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea3d9a3991748c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Architect</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Intelex</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9addd16d08dc466</t>
+          <t>https://www.indeed.com/viewjob?jk=a43228eca462ffe2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Sprouts Farmers Market</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b9e656d2a85bee5</t>
+          <t>https://www.indeed.com/viewjob?jk=be1d2f0b19c98908</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform Operations Engineer (Site Reliability Engineer)</t>
+          <t>AI Automation Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Kinesis, IAM, RDS, Azure, Event Hubs, Google Cloud Platform, GCP, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0928cac745f837eb</t>
+          <t>https://www.indeed.com/viewjob?jk=36099f55f9dfc1ab</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8327d885674c2cb</t>
+          <t>https://www.indeed.com/viewjob?jk=f08447131564025e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Python / DevOps / Message Brokers</t>
+          <t>Data &amp; Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, Unity Catalog, Spark, PySpark, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ccd83a736eef1f</t>
+          <t>https://www.indeed.com/viewjob?jk=8627b9fa5d939b34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT Data Architect (Senior/Specialist)</t>
+          <t>Senior Cloud Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State of Washington</t>
+          <t>Intelex</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tumwater, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, S3, ECS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147df69fbd3dc06f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9addd16d08dc466</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6c83582ab47968</t>
+          <t>https://www.indeed.com/viewjob?jk=2b9e656d2a85bee5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Operations Engineer (Site Reliability Engineer)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>iManage</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
+          <t>https://www.indeed.com/viewjob?jk=0928cac745f837eb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,42 +1091,42 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adaf2ea98a3a0c98</t>
+          <t>https://www.indeed.com/viewjob?jk=b8327d885674c2cb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer - Python / DevOps / Message Brokers</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51bef44ce851670</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ccd83a736eef1f</t>
         </is>
       </c>
     </row>
@@ -1138,90 +1138,90 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Brookfield Properties</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572a735d26988840</t>
+          <t>https://www.indeed.com/viewjob?jk=eb497e82428572d4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Python &amp; SAS Developer (Data Modernization)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Illumen Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, IAM, RDS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea308d3aa4efb3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=d892ead602b58795</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IT Data Architect (Senior/Specialist)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>State of Washington</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tumwater, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17688e9ed438da93</t>
+          <t>https://www.indeed.com/viewjob?jk=147df69fbd3dc06f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625378a8c8feabb6</t>
+          <t>https://www.indeed.com/viewjob?jk=cc6c83582ab47968</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4edea8f81b8bef39</t>
+          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Full Swing Golf Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a345b3fc59984aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539dcfcd9f0b442c</t>
+          <t>https://www.indeed.com/viewjob?jk=04ed95a8ab7c02d2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eda110060bcf3d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>iManage</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=007b85bce01910b5</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a78f0b7d9a954</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Hiring Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d6b68e20522b555</t>
+          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Security Engineer/DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>GetWellNetwork</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f193252272c1cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,172 +1546,172 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06003d92ed7c2087</t>
+          <t>https://www.indeed.com/viewjob?jk=37aff8f440d6ba6d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure / Dev Ops Engineer</t>
+          <t>Software Engineer, Geospatial Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Full Swing Golf Inc</t>
+          <t>Civitech</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e2bb60d0f9bd54</t>
+          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Scientific Games</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04ed95a8ab7c02d2</t>
+          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Application Developer – Data &amp; Digital Solutions</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>TC Energy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66d572a44ce5cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer/DevSecOps Engineer</t>
+          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GetWellNetwork</t>
+          <t>Quisitive</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f8ca36b295c24d</t>
+          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AWS Full Stack Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hiring Group</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Databricks, Scala, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc54c80bec441143</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Recursion Technologies, Inc</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Azure Cosmos DB, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52874955a1d8a7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer, Geospatial Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Civitech</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9d28890cbb8b4f4</t>
+          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Application Developer – Data &amp; Digital Solutions</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TC Energy</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b192109a8d9de9</t>
+          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Azure &amp; Microsoft Fabric</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56fe4f99d705b6f4</t>
+          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>iHeartMedia</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
+          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>K&amp;L GATES</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
+          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MPR Management</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Flint, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>K&amp;L GATES</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, Dimensional Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd2e06fdde37fe</t>
+          <t>https://www.indeed.com/viewjob?jk=30803e9edf7f7cc6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adebbeb79bcc9a1c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>iHeartMedia</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>Redshift, RDS, BigQuery, Hive, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf9760e71980916f</t>
+          <t>https://www.indeed.com/viewjob?jk=356a68911d5f594b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>MPR Management</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Flint, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94cb48d5ed1c52af</t>
+          <t>https://www.indeed.com/viewjob?jk=6631941e87630a58</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbc89f3bdee8ad93</t>
+          <t>https://www.indeed.com/viewjob?jk=df86eb0af63d38af</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. Solutions Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>GEM Technologies, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Los Alamos, NM, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c02b3eae0c4832e</t>
+          <t>https://www.indeed.com/viewjob?jk=a20d25715f64218c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da723ed84459a1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>SW Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Highlands Ranch, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Snowflake, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2dcb8f1f90f8bd</t>
+          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>OMS Medical Billing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,77 +2271,77 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=418149d6683bca23</t>
+          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (AI &amp; Analytics) - Hybrid</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e156b33a61bb6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect</t>
+          <t>GD169 Senior Software Systems Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEM Technologies, Inc.</t>
+          <t>ADNET Systems, Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Alamos, NM, US USA</t>
+          <t>Greenbelt, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Lambda, S3, Scala, Dask, DynamoDB, ELT, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20d25715f64218c</t>
+          <t>https://www.indeed.com/viewjob?jk=f02363682eba87a1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>AI QA Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Comtek Intl</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d22bd46597ab543</t>
+          <t>https://www.indeed.com/viewjob?jk=956ec640e084971c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SW Engineer</t>
+          <t>Specialist Solutions Architect - GCP Infrastructure</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Maven, Docker</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df58d72b6ebba2f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f18ddccc944039f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>OMS Medical Billing</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Databricks, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ELT, CI/CD, Docker</t>
+          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6f2596747788c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer - Albany</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rocket Science Group</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=919305a6d33188b3</t>
+          <t>https://www.indeed.com/viewjob?jk=66ed44d25f7a706b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DevOps Software Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tommy Car Wash</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Holland, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20c20616163c8dea</t>
+          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI QA Architect</t>
+          <t>Software Engineer II - UnderwritingCenter</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Comtek Intl</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956ec640e084971c</t>
+          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - GCP Infrastructure</t>
+          <t>Data Engineer - Operational Support (Co-op)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f18ddccc944039f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GD169 Senior Software Systems Engineer &amp; Architect</t>
+          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ADNET Systems, Inc</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Greenbelt, MD, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Dask, DynamoDB, ELT, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02363682eba87a1</t>
+          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Developer Sr. - AI-Native .NET/ Azure (Cloud Platform)</t>
+          <t>Sr. Data Engineer (Hartford, CT)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, MongoDB, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db55be048a80c25e</t>
+          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer (Hybrid)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191abb774c4fc1ef</t>
+          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer II - UnderwritingCenter</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b18b7116a0216a</t>
+          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hartford, CT)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Bridgepointe Technologies</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, HDFS, Hive, Spark, PySpark, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e768638b0d15ea6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e6e1623e260b65</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cac895741d0c5e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Stock Yards Bank &amp; Trust</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Databricks, Hive, Spark, Scala, Snowflake, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=324abf6ed6a12661</t>
+          <t>https://www.indeed.com/viewjob?jk=ce0334c84fa0af8d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>IT Platform Architect - Network</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>International Paper</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Splunk, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e0436b74d002fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d26050fc54720f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Operational Support (Co-op)</t>
+          <t>Data Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Mango Chamba, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ad7172da2d3793</t>
+          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer – Agentic AI &amp; ML Ops (Co-op)</t>
+          <t>Product Software Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50bca42b0ee032c9</t>
+          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bridgepointe Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e6e1623e260b65</t>
+          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineers (Golang/Java)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Stock Yards Bank &amp; Trust</t>
+          <t>TECHNOLOGENT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Star Schema, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce0334c84fa0af8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Architect (Snowflake)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mango Chamba, LLC</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=495f4d3d488629b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7287ccdf3b9a75d9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Product Software Engineer II</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Paylink Direct</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46198227fa92bca6</t>
+          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799f6c78471ba72a</t>
+          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineers (Golang/Java)</t>
+          <t>Data Engineer - Fabric</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TECHNOLOGENT</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, HBase, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9dbff6f9b9b55eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AmeriGas</t>
+          <t>Calder</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Internship – Data Engineer, Commercial Audience Science (Spring 2027)</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>Peterson Holding</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29c16dbcddbb923</t>
+          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Paylink Direct</t>
+          <t>AmeriGas</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>RDS, Data Factory, Synapse Analytics, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d48ca7baf014b40f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb83a57c0a41012e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00b7b67359ffc44</t>
+          <t>https://www.indeed.com/viewjob?jk=920269b0f09e721a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Calder</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f8d0096c255500e</t>
+          <t>https://www.indeed.com/viewjob?jk=3da2910a4a341974</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Peterson Holding</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=645b5d2c574a7492</t>
+          <t>https://www.indeed.com/viewjob?jk=58b9443c79a19e0d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kash Tech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ab6dcdf3386d55</t>
+          <t>https://www.indeed.com/viewjob?jk=b88f4a4b03b9105e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Services Architect - New York</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a22e754adf0a78bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec034d4d2c0659b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full-Stack Developer (Java, React, Oracle/MySQL, DevOps)</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Netbuilder</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b19eed4d204d2f13</t>
+          <t>https://www.indeed.com/viewjob?jk=c012e7a73c63b98f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>USI Insurance Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Kimball, Snowflake Schema, ELT, dbt, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2106609d886859e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8efd67ad513c0fe2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff87cc807f59577</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SQL AND ETL DEVELOPER</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,472 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44a0a9b3d5879441</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=874c25ddadc07b4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf72861040f23682</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91f24b220aab5d6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99c249a8e72b3138</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Annapolis, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3e749bf18c9ccc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Systems Architect</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MACOM Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Lowell, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=022e7efd7d261246</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Business Intelligence Architect</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Kash Tech</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06ab6dcdf3386d55</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Services Architect - New York</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Datadog</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a22e754adf0a78bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Full-Stack Developer (Java, React, Oracle/MySQL, DevOps)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Netbuilder</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, MySQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b19eed4d204d2f13</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Data Warehouse Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>USI Insurance Services</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Kimball, Snowflake Schema, ELT, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2106609d886859e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MS Fabric</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ec086aef45de637</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SQL AND ETL DEVELOPER</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>RDS, Azure, Snowflake, SQL Server, MongoDB, Cassandra, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=de66891cd1166601</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fb03ca29667d8d5</t>
         </is>
       </c>
     </row>
